--- a/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
+++ b/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
@@ -297,114 +297,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="75" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="10" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B1" s="10" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="10" t="str">
-        <x:v>values</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B2" s="7" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" s="7" t="str">
-        <x:v>(list#sep=;),AttributeValue</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="8" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B3" s="8"/>
-      <x:c r="C3" s="8"/>
-      <x:c r="D3" s="8"/>
-    </x:row>
-    <x:row r="4" ht="65" customHeight="1">
-      <x:c r="A4" s="9" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="str">
-        <x:v>方案ID</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
-        <x:v>调试用途</x:v>
-      </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>属性ID:数值；分号分隔，必需属性全量填写</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="52" customHeight="1">
-      <x:c r="A5" s="4"/>
-      <x:c r="B5" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
-        <x:v>玩家闭环调试</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="str">
-        <x:v>1:100;2:20;3:0;4:4;5:1;6:1;7:100;8:0;9:1;10:1;11:0;12:100;13:1;14:1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="52" customHeight="1">
-      <x:c r="A6" s="4"/>
-      <x:c r="B6" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="str">
-        <x:v>近战怪闭环调试</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="str">
-        <x:v>1:40;2:8;3:0;4:2;5:1;6:1;7:100;8:0;9:1;10:1;11:0;12:100;13:1;14:1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="52" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="str">
-        <x:v>玩家概率压测</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="str">
-        <x:v>1:100;2:20;3:0;4:4;5:1;6:1;7:100;8:25;9:1;10:1;11:25;12:100;13:1;14:1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="52" customHeight="1">
-      <x:c r="A8" s="4"/>
-      <x:c r="B8" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="str">
-        <x:v>近战怪概率压测</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="str">
-        <x:v>1:40;2:8;3:0;4:2;5:1;6:1;7:100;8:25;9:1;10:1;11:25;12:100;13:1;14:1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="75" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="10" t="str">
+        <v>##</v>
+      </c>
+      <c r="B1" s="10" t="str">
+        <v>id</v>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v>name</v>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="7" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B2" s="7" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>(list#sep=;),AttributeValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="8" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="9" t="str">
+        <v>##</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <v>方案ID</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <v>调试用途</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>属性ID:放大1000倍的整数值，以分号分隔；实际属性值=表值/1000；最多3位小数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <v>玩家闭环调试</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <v>近战怪闭环调试</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <v>玩家概率压测</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <v>近战怪概率压测</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
+++ b/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="R3dfb9d3eadd1481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="Rdde9f8b820f04e60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +33,42 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,14 +95,48 @@
         <x:fgColor rgb="FFF6F8FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -96,6 +164,67 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -297,128 +426,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="75" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="10" t="str">
-        <v>##</v>
-      </c>
-      <c r="B1" s="10" t="str">
-        <v>id</v>
-      </c>
-      <c r="C1" s="10" t="str">
-        <v>name</v>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="7" t="str">
-        <v>##type</v>
-      </c>
-      <c r="B2" s="7" t="str">
-        <v>int</v>
-      </c>
-      <c r="C2" s="7" t="str">
-        <v>string</v>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>(list#sep=;),AttributeValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="8" t="str">
-        <v>##var</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" ht="65" customHeight="1">
-      <c r="A4" s="9" t="str">
-        <v>##</v>
-      </c>
-      <c r="B4" s="9" t="str">
-        <v>方案ID</v>
-      </c>
-      <c r="C4" s="9" t="str">
-        <v>调试用途</v>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>属性ID:放大1000倍的整数值，以分号分隔；实际属性值=表值/1000；最多3位小数</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="str">
-        <v>玩家闭环调试</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="str">
-        <v>近战怪闭环调试</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <v>玩家概率压测</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="str">
-        <v>近战怪概率压测</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="20" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B1" s="20" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="20" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="D1" s="20" t="str">
+        <x:v>values</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="22" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="22" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2" s="22" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D2" s="22" t="str">
+        <x:v>(list#sep=;),AttributeValue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="24" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B3" s="24"/>
+      <x:c r="C3" s="24"/>
+      <x:c r="D3" s="24"/>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="26" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="26" t="str">
+        <x:v>方案ID</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="str">
+        <x:v>调试用途</x:v>
+      </x:c>
+      <x:c r="D4" s="26" t="str">
+        <x:v>属性ID:放大1000倍的整数值，以分号分隔；实际属性值=表值/1000；最多3位小数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="52" customHeight="1">
+      <x:c r="A5" s="31"/>
+      <x:c r="B5" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>玩家闭环调试</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="52" customHeight="1">
+      <x:c r="A6" s="31"/>
+      <x:c r="B6" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>近战怪闭环调试</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="31"/>
+      <x:c r="B7" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>玩家概率压测</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="31"/>
+      <x:c r="B8" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>近战怪概率压测</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31"/>
+      <x:c r="B9" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>M1标准地面怪</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="31"/>
+      <x:c r="B10" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C10" s="31" t="str">
+        <x:v>M1轻型飞行怪</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="str">
+        <x:v>1:30000;2:7000;3:0;4:2600;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="31"/>
+      <x:c r="B11" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C11" s="31" t="str">
+        <x:v>M1慢速高血怪</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="str">
+        <x:v>1:65000;2:10000;3:0;4:1500;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31"/>
+      <x:c r="B12" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="31" t="str">
+        <x:v>M1快速高攻怪</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="str">
+        <x:v>1:50000;2:12000;3:0;4:2200;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31"/>
+      <x:c r="B13" s="31" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C13" s="31" t="str">
+        <x:v>M1最终Boss</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="str">
+        <x:v>1:3000000;2:12000;3:5000;4:1600;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
+++ b/Config/Datas/Tables/s_属性方案_AttributeProfileConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="Rdde9f8b820f04e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbAttributeProfile" sheetId="1" r:id="R3f2400d412a74d3d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -494,7 +494,7 @@
         <x:v>玩家闭环调试</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
-        <x:v>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="52" customHeight="1">
@@ -506,7 +506,7 @@
         <x:v>近战怪闭环调试</x:v>
       </x:c>
       <x:c r="D6" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
@@ -518,7 +518,7 @@
         <x:v>玩家概率压测</x:v>
       </x:c>
       <x:c r="D7" s="31" t="str">
-        <x:v>1:100000;2:20000;3:0;4:4000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:100000;2:20000;3:0;4:400000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
@@ -530,7 +530,7 @@
         <x:v>近战怪概率压测</x:v>
       </x:c>
       <x:c r="D8" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:25000;9:1000;10:1000;11:25000;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -542,7 +542,7 @@
         <x:v>M1标准地面怪</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>1:40000;2:8000;3:0;4:2000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:40000;2:8000;3:0;4:100000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -554,7 +554,7 @@
         <x:v>M1轻型飞行怪</x:v>
       </x:c>
       <x:c r="D10" s="31" t="str">
-        <x:v>1:30000;2:7000;3:0;4:2600;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:30000;2:7000;3:0;4:130000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -566,7 +566,7 @@
         <x:v>M1慢速高血怪</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>1:65000;2:10000;3:0;4:1500;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:65000;2:10000;3:0;4:75000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -578,7 +578,7 @@
         <x:v>M1快速高攻怪</x:v>
       </x:c>
       <x:c r="D12" s="31" t="str">
-        <x:v>1:50000;2:12000;3:0;4:2200;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:50000;2:12000;3:0;4:110000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -590,7 +590,7 @@
         <x:v>M1最终Boss</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
-        <x:v>1:3000000;2:12000;3:5000;4:1600;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
+        <x:v>1:3000000;2:12000;3:5000;4:80000;5:1000;6:1000;7:100000;8:0;9:1000;10:1000;11:0;12:100000;13:1000;14:1000</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
